--- a/examples/Excel_Compatibility_Challenge.xlsx
+++ b/examples/Excel_Compatibility_Challenge.xlsx
@@ -4,14 +4,22 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Financial Model" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Lookup Tables" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Dynamic Arrays" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Analysis" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Errors" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+  <si>
+    <t>Year</t>
+  </si>
   <si>
     <t>Revenue</t>
   </si>
@@ -19,17 +27,120 @@
     <t>Costs</t>
   </si>
   <si>
-    <t>Profit</t>
+    <t>Operating profit</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Net profit</t>
+  </si>
+  <si>
+    <t>Net present value</t>
+  </si>
+  <si>
+    <t>Nested decision</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Revenue growth</t>
+  </si>
+  <si>
+    <t>Cost ratio</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>Initial revenue</t>
+  </si>
+  <si>
+    <t>Start date</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>Notebook</t>
+  </si>
+  <si>
+    <t>P200</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>P300</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Exact lookup</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>Filtered prices</t>
+  </si>
+  <si>
+    <t>LET calculation</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Deliberate errors</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00)"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -37,13 +148,23 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF217346"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,8 +179,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -75,6 +199,211 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and net profit</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Financial Model'!A2:A6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Financial Model'!B2:B6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>134400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150528</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>168591.36000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>188822.32320000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Net profit</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4DAA77"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Financial Model'!A2:A6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2030</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Financial Model'!F2:F6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>39816</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44593.92</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>49945.19040000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55938.61324800001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62651.246837760016</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="100"/>
+        <c:axId val="200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="200"/>
+        <c:crosses val="autoZero"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/openexcelDrawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6191250" cy="2857500"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdChart1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -399,63 +728,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="2">
+        <f>'Assumptions'!$B$6</f>
+        <v>120000</v>
+      </c>
+      <c r="C2" s="2">
+        <f>B2*'Assumptions'!$B$3</f>
+        <v>69600</v>
+      </c>
+      <c r="D2" s="2">
+        <f>B2-C2</f>
+        <v>50400</v>
+      </c>
+      <c r="E2" s="2">
+        <f>D2*'Assumptions'!$B$4</f>
+        <v>10584</v>
+      </c>
+      <c r="F2" s="2">
+        <f>D2-E2</f>
+        <v>39816</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2027</v>
+      </c>
+      <c r="B3" s="2">
+        <f>B2*(1+'Assumptions'!$B$2)</f>
+        <v>134400</v>
+      </c>
+      <c r="C3" s="2">
+        <f>B3*'Assumptions'!$B$3</f>
+        <v>77952</v>
+      </c>
+      <c r="D3" s="2">
+        <f>B3-C3</f>
+        <v>56448</v>
+      </c>
+      <c r="E3" s="2">
+        <f>D3*'Assumptions'!$B$4</f>
+        <v>11854.08</v>
+      </c>
+      <c r="F3" s="2">
+        <f>D3-E3</f>
+        <v>44593.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2028</v>
+      </c>
+      <c r="B4" s="2">
+        <f>B3*(1+'Assumptions'!$B$2)</f>
+        <v>150528</v>
+      </c>
+      <c r="C4" s="2">
+        <f>B4*'Assumptions'!$B$3</f>
+        <v>87306.23999999999</v>
+      </c>
+      <c r="D4" s="2">
+        <f>B4-C4</f>
+        <v>63221.76000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <f>D4*'Assumptions'!$B$4</f>
+        <v>13276.5696</v>
+      </c>
+      <c r="F4" s="2">
+        <f>D4-E4</f>
+        <v>49945.19040000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2029</v>
+      </c>
+      <c r="B5" s="2">
+        <f>B4*(1+'Assumptions'!$B$2)</f>
+        <v>168591.36000000002</v>
+      </c>
+      <c r="C5" s="2">
+        <f>B5*'Assumptions'!$B$3</f>
+        <v>97782.9888</v>
+      </c>
+      <c r="D5" s="2">
+        <f>B5-C5</f>
+        <v>70808.37120000001</v>
+      </c>
+      <c r="E5" s="2">
+        <f>D5*'Assumptions'!$B$4</f>
+        <v>14869.757952000002</v>
+      </c>
+      <c r="F5" s="2">
+        <f>D5-E5</f>
+        <v>55938.61324800001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2030</v>
+      </c>
+      <c r="B6" s="2">
+        <f>B5*(1+'Assumptions'!$B$2)</f>
+        <v>188822.32320000004</v>
+      </c>
+      <c r="C6" s="2">
+        <f>B6*'Assumptions'!$B$3</f>
+        <v>109516.94745600002</v>
+      </c>
+      <c r="D6" s="2">
+        <f>B6-C6</f>
+        <v>79305.37574400002</v>
+      </c>
+      <c r="E6" s="2">
+        <f>D6*'Assumptions'!$B$4</f>
+        <v>16654.128906240003</v>
+      </c>
+      <c r="F6" s="2">
+        <f>D6-E6</f>
+        <v>62651.246837760016</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <f>NPV('Assumptions'!B5,F2:F6)</f>
+        <v>198502.80438781853</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IFERROR(IF(AVERAGE(F2:F6)&gt;40000,"Healthy","Review"),"Check inputs")</f>
+        <v>Healthy</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rIdOpenExcelChart"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46023</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <f>XLOOKUP("P200",A2:A4,C2:C4)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f>VLOOKUP("P300",A2:C4,3,FALSE)</f>
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>SEQUENCE(5,3,1,1)</f>
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>125000</v>
-      </c>
-      <c r="B2">
-        <v>70000</v>
+      <c r="E2">
+        <f>FILTER('Lookup Tables'!C2:C4,'Lookup Tables'!C2:C4&gt;20)</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f>LET(revenue,120000,cost,70000,revenue-cost)</f>
+        <v>50000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
-        <f>A2-B2</f>
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>150000</v>
-      </c>
-      <c r="B3">
-        <v>82000</v>
+        <v>120</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2">
+        <v>150</v>
+      </c>
+      <c r="H2">
+        <v>160</v>
+      </c>
+      <c r="I2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
       </c>
       <c r="C3">
-        <f>A3-B3</f>
-        <v>68000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>175000</v>
-      </c>
-      <c r="B4">
-        <v>91000</v>
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3">
+        <v>95</v>
+      </c>
+      <c r="H3">
+        <v>140</v>
+      </c>
+      <c r="I3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
       </c>
       <c r="C4">
-        <f>A4-B4</f>
-        <v>84000</v>
+        <v>160</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4">
+        <v>245</v>
+      </c>
+      <c r="H4">
+        <v>300</v>
+      </c>
+      <c r="I4">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
-        <f>SUM(C2:C4)</f>
-        <v>207000</v>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="e">
+        <f>1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="e">
+        <f>UNKNOWNFUNCTION(1)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="e">
+        <f>A5</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="e">
+        <f>A4</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="e">
+        <f>SQRT(-1)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>IFERROR(A2,"Handled")</f>
+        <v>Handled</v>
       </c>
     </row>
   </sheetData>
